--- a/TEngine/Configs/GameConfig/Datas/__tables__.xlsx
+++ b/TEngine/Configs/GameConfig/Datas/__tables__.xlsx
@@ -533,7 +533,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K8"/>
+  <dimension ref="A1:K9"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="28" bestFit="1" customWidth="1"/>
@@ -703,6 +703,36 @@
         <v>41</v>
       </c>
     </row>
+    <row r="9" ht="26" customHeight="1">
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">trophy.TbTrophy</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ConfTrophy</t>
+        </is>
+      </c>
+      <c r="D9" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Trophy.xlsx</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">c</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">月度每日挑战奖杯</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
   <hyperlinks>
